--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -614,6 +614,12 @@
   </x:si>
   <x:si>
     <x:t>desc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cellSize</x:t>
+  </x:si>
+  <x:si>
+    <x:t>一个格子的世界边长（单位：米）。必须与 EGB 网格预制体的 cellSize 一致（当前 2）；模型导入后处理按它把建筑缩放到 footprint 对应的格数</x:t>
   </x:si>
   <x:si>
     <x:t>totalLevels</x:t>
@@ -1732,7 +1738,7 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>10</x:v>
@@ -1741,12 +1747,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
@@ -1755,12 +1761,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>10</x:v>
@@ -1769,12 +1775,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
@@ -1783,12 +1789,12 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
@@ -1797,7 +1803,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3232,7 +3238,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D9"/>
+  <x:dimension ref="A1:D10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="25.139196" style="0" customWidth="1"/>
@@ -3260,10 +3266,10 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>198</x:v>
@@ -3274,10 +3280,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>200</x:v>
@@ -3288,7 +3294,7 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>0</x:v>
@@ -3330,10 +3336,10 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>208</x:v>
@@ -3344,10 +3350,10 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>210</x:v>
@@ -3358,13 +3364,27 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>213</x:v>
+      <x:c r="C10" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>215</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3406,7 +3426,7 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>10</x:v>
@@ -3415,12 +3435,12 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
@@ -3429,12 +3449,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>10</x:v>
@@ -3443,12 +3463,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
@@ -3457,12 +3477,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
@@ -3471,7 +3491,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -58,13 +58,13 @@
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>作用半径（格，切比雪夫距离，自占地边缘起算；邻接计分默认用本建筑半径；0=待定）</x:t>
+    <x:t>作用半径（格，球形欧氏距离，自占地边缘起算；邻接计分默认用本建筑半径）。§11 建议范围档位换算：小=3 / 中=5 / 大=7 / 极大=10</x:t>
   </x:si>
   <x:si>
     <x:t>baseScore</x:t>
   </x:si>
   <x:si>
-    <x:t>基础分（落地即得；0=待定）</x:t>
+    <x:t>基础分（落地即得）</x:t>
   </x:si>
   <x:si>
     <x:t>elementBonus</x:t>
@@ -136,7 +136,7 @@
     <x:t>TRUE</x:t>
   </x:si>
   <x:si>
-    <x:t>1|1|1|1|1|1</x:t>
+    <x:t>1|1.1|1.25|1.5|1.8|2.2</x:t>
   </x:si>
   <x:si>
     <x:t>windmill</x:t>
@@ -163,7 +163,7 @@
     <x:t>势能塔</x:t>
   </x:si>
   <x:si>
-    <x:t>anchor:0|giantWindmill:0</x:t>
+    <x:t>anchor:20|giantWindmill:30</x:t>
   </x:si>
   <x:si>
     <x:t>sail</x:t>
@@ -178,7 +178,7 @@
     <x:t>FALSE</x:t>
   </x:si>
   <x:si>
-    <x:t>0|0|0|0|0|0</x:t>
+    <x:t>0|10|20|35|55|80</x:t>
   </x:si>
   <x:si>
     <x:t>miningStation</x:t>
@@ -193,7 +193,7 @@
     <x:t>oreRange</x:t>
   </x:si>
   <x:si>
-    <x:t>ore:0</x:t>
+    <x:t>ore:25</x:t>
   </x:si>
   <x:si>
     <x:t>workshop</x:t>
@@ -211,7 +211,7 @@
     <x:t>floatingZone</x:t>
   </x:si>
   <x:si>
-    <x:t>anchor:0:1</x:t>
+    <x:t>anchor:40:1</x:t>
   </x:si>
   <x:si>
     <x:t>-150|30|60|120|240|480</x:t>
@@ -250,7 +250,7 @@
     <x:t>residential</x:t>
   </x:si>
   <x:si>
-    <x:t>giantWindmill:0</x:t>
+    <x:t>giantWindmill:30</x:t>
   </x:si>
   <x:si>
     <x:t>residence</x:t>
@@ -259,6 +259,9 @@
     <x:t>居民区</x:t>
   </x:si>
   <x:si>
+    <x:t>0|0|0|0|-20|-50</x:t>
+  </x:si>
+  <x:si>
     <x:t>logisticsPoint</x:t>
   </x:si>
   <x:si>
@@ -268,7 +271,7 @@
     <x:t>logistics</x:t>
   </x:si>
   <x:si>
-    <x:t>anchor:0</x:t>
+    <x:t>anchor:15</x:t>
   </x:si>
   <x:si>
     <x:t>logisticsHub</x:t>
@@ -295,7 +298,7 @@
     <x:t>prefabPath</x:t>
   </x:si>
   <x:si>
-    <x:t>表现 Prefab 路径（Resources 相对路径或 Addressables key，表现层统一口径；空=白模占位）</x:t>
+    <x:t>表现 Prefab 路径（Resources 相对路径或 Addressables key，表现层统一口径；空=白模占位）。由菜单 Tools/美术/生成白模 Prefab 从 Assets/Res/&lt;资产名&gt;/fbx/ 批量生成到 Assets/Resources/Prefab/Building/</x:t>
   </x:si>
   <x:si>
     <x:t>windVane_01</x:t>
@@ -304,148 +307,199 @@
     <x:t>#</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/windVane_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>windmill_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>##|##</x:t>
+  </x:si>
+  <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>windmill_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>##|##</x:t>
-  </x:si>
-  <x:si>
     <x:t>farm_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/farm_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>potentialTower_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/potentialTower_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>sail_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/sail_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>miningStation_01</x:t>
   </x:si>
   <x:si>
     <x:t>##</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/miningStation_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>workshop_01</x:t>
   </x:si>
   <x:si>
     <x:t>###|###|###</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/workshop_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>dock_01</x:t>
   </x:si>
   <x:si>
     <x:t>######|######|######|######|######|######</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/dock_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>granary_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/granary_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>restaurant_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/restaurant_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>shop_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/shop_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>citizenCenter_01</x:t>
   </x:si>
   <x:si>
     <x:t>####|####|####|####</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/citizenCenter_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>residence_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/residence_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>residence_02</x:t>
   </x:si>
   <x:si>
     <x:t>###|#..</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/residence_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>residence_03</x:t>
   </x:si>
   <x:si>
     <x:t>#.#|###</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/residence_03</x:t>
+  </x:si>
+  <x:si>
     <x:t>logisticsPoint_01</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Building/logisticsPoint_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>logisticsHub_01</x:t>
   </x:si>
   <x:si>
-    <x:t>结算建筑 Id（主键 → Building 表）。本行描述'它因附近什么建筑而加/扣分'；方向不可反读：A 因 B 加分不代表 B 因 A 加分（§13.1），双向关系要在两行各写一条</x:t>
+    <x:t>Prefab/Building/logisticsHub_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>结算建筑 Id（主键 → Building 表）。关系有向：本行只描述「本建筑因周围有谁而加/扣分」，反向要在对方行里再写一条（§13 结算原则）</x:t>
   </x:si>
   <x:si>
     <x:t>bonusFrom</x:t>
   </x:si>
   <x:si>
-    <x:t>加分来源：来源Id:分值[:上限]，多个用|分隔。上限=最多计入个数（省略或0=不限，居民区上限见§12.13、物流点专属建议2个§10.7）。判定范围一律用本建筑的 radius。来源=自己表示同类聚集加分。例 restaurant:10:2</x:t>
+    <x:t>加分来源：来源Id:分值[:上限]，多个用|分隔。上限=最多计入几个来源，省略/0=不限。来源填自己=同类聚集加分（如 residence:8:4）。判定范围一律用本建筑 Building.radius</x:t>
   </x:si>
   <x:si>
     <x:t>penaltyFrom</x:t>
   </x:si>
   <x:si>
-    <x:t>扣分来源：格式同左，分值填正数=扣多少分。来源=自己表示同类排斥（§15），判定范围同样用本建筑的 radius。空=无扣分关系</x:t>
-  </x:si>
-  <x:si>
-    <x:t>residence:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windVane:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>farm:0|potentialTower:0|workshop:0|logisticsPoint:0:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windmill:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windmill:0|farm:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windmill:0|workshop:0|logisticsPoint:0:2|logisticsHub:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>potentialTower:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>miningStation:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>miningStation:0|logisticsPoint:0:2|logisticsHub:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>workshop:0|logisticsPoint:0:2|logisticsHub:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>farm:0|logisticsPoint:0:2|logisticsHub:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>workshop:0|restaurant:0|residence:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>citizenCenter:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>restaurant:0:2|shop:0:2|citizenCenter:0:1|residence:0:4|logisticsPoint:0:2|logisticsHub:0:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>miningStation:0|workshop:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>logisticsPoint:0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>logisticsHub:0</x:t>
+    <x:t>扣分来源：格式同上，分值填正数表示扣多少分。来源填自己=同类拥挤惩罚（§15）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>windVane:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>farm:12|potentialTower:8|workshop:8|logisticsPoint:10:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>windmill:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>windmill:12|farm:6:4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>windmill:10|workshop:8|logisticsPoint:10:2|logisticsHub:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>potentialTower:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>miningStation:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>miningStation:15|logisticsPoint:10:2|logisticsHub:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>workshop:10|logisticsPoint:10:2|logisticsHub:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>farm:12|logisticsPoint:10:2|logisticsHub:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>workshop:8|restaurant:8|residence:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>citizenCenter:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>restaurant:12:2|shop:12:2|citizenCenter:20:1|residence:8:4|logisticsPoint:10:2|logisticsHub:15:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>miningStation:15|workshop:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>logisticsPoint:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>logisticsPoint:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>logisticsHub:30</x:t>
   </x:si>
   <x:si>
     <x:t>elementId</x:t>
   </x:si>
   <x:si>
-    <x:t>地图元素 Id（主键，camelCase，被 BuildingMapElement/Building.placement 引用）</x:t>
+    <x:t>地图元素 Id（主键，camelCase，被 Building.elementBonus 与地图 JSON 引用，一字不差）</x:t>
   </x:si>
   <x:si>
     <x:t>占地形状掩码：每个元素是一行（自上而下）、|分隔，#=占用 .=空，各行长度须一致。如巨型风车 4×4=####|####|####|####，1×1=#。island/floatingZone 为区域填充地形，本列不启用（填 #）</x:t>
@@ -457,13 +511,22 @@
     <x:t>countMin</x:t>
   </x:si>
   <x:si>
-    <x:t>地图生成数量下限（巨型风车固定 1；windSource 即初始风数量 §20；0=待定）</x:t>
+    <x:t>地图生成数量下限（巨型风车固定 1；windSource 即初始风数量 §20；0=不生成）</x:t>
   </x:si>
   <x:si>
     <x:t>countMax</x:t>
   </x:si>
   <x:si>
-    <x:t>地图生成数量上限（0=待定；island/floatingZone 为区域填充，数量列可不启用）</x:t>
+    <x:t>地图生成数量上限（island/floatingZone 为区域填充，数量列不启用填 0）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>isTerrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>是否可刷地形：TRUE=1×1 区域填充地形，地图编辑器刷子调色板只列出本列为 TRUE 的行；FALSE=多格元素或点元素，走摆放流程不走刷子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>表现 Prefab 路径（Resources 相对路径，与 BuildingVariant.prefabPath 同口径；空=无独立模型，地形类元素靠地形层着色表现）。由菜单 Tools/美术/生成白模 Prefab 生成到 Assets/Resources/Prefab/Element/</x:t>
   </x:si>
   <x:si>
     <x:t>giantWindmill</x:t>
@@ -472,18 +535,27 @@
     <x:t>巨型风车</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Element/giantWindmill</x:t>
+  </x:si>
+  <x:si>
     <x:t>anchor</x:t>
   </x:si>
   <x:si>
     <x:t>锚点</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Element/anchor</x:t>
+  </x:si>
+  <x:si>
     <x:t>ore</x:t>
   </x:si>
   <x:si>
     <x:t>矿藏</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Element/ore</x:t>
+  </x:si>
+  <x:si>
     <x:t>绿地</x:t>
   </x:si>
   <x:si>
@@ -544,7 +616,7 @@
     <x:t>unlockCost</x:t>
   </x:si>
   <x:si>
-    <x:t>解锁本级费用（金币；第 1 级免费=0，随等级递增 §4.1；0=待定）</x:t>
+    <x:t>解锁本级费用（金币；第 1 级免费=0，随等级递增 §4.1）</x:t>
   </x:si>
   <x:si>
     <x:t>groupCount</x:t>
@@ -568,7 +640,67 @@
     <x:t>pool</x:t>
   </x:si>
   <x:si>
-    <x:t>本级抽取池：变体Id:数量，多条用|分隔（变体Id → BuildingVariant 表主键，配到占地结构粒度；数量=该建筑在本级池中的份数，同组可重复 §4.2）。例 residence_01:2|farm_01:3。空=待设计</x:t>
+    <x:t>本级抽取池：变体Id:数量，多条用|分隔（变体Id → BuildingVariant 表主键，配到占地结构粒度；数量=该建筑在本级池中的份数，同组可重复 §4.2）。例 residence_01:2|farm_01:3。池按等级渐进解锁：前期只放 placement=any 的易放建筑，后期才引入需要绿地/矿藏/浮空区域的限制建筑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:4|residence_02:2|workshop_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:4|residence_02:3|residence_03:2|workshop_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|residence_02:3|residence_03:3|workshop_01:2|windmill_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|residence_02:2|residence_03:2|workshop_01:2|windmill_01:3|farm_01:3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|residence_02:2|residence_03:2|workshop_01:2|windmill_01:3|farm_01:4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|residence_03:2|workshop_01:2|windmill_01:2|farm_01:3|granary_01:3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|residence_02:2|workshop_01:2|farm_01:3|granary_01:3|miningStation_01:3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|residence_03:2|workshop_01:3|windmill_01:2|miningStation_01:3|logisticsPoint_01:3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|residence_02:2|workshop_01:2|granary_01:2|miningStation_01:2|logisticsPoint_01:3|restaurant_01:3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|residence_03:3|restaurant_01:3|shop_01:3|logisticsPoint_01:2|workshop_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_02:3|residence_03:2|restaurant_01:3|shop_01:3|potentialTower_01:3|windmill_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:2|restaurant_01:2|shop_01:3|potentialTower_01:3|logisticsPoint_01:2|granary_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_03:3|potentialTower_01:3|sail_01:3|windmill_01:2|workshop_01:2|logisticsPoint_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:2|sail_01:3|dock_01:2|potentialTower_01:2|shop_01:2|granary_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_02:2|sail_01:2|dock_01:3|logisticsPoint_01:3|workshop_01:2|restaurant_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|citizenCenter_01:2|dock_01:2|shop_01:2|restaurant_01:2|potentialTower_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_03:3|citizenCenter_01:2|logisticsHub_01:2|logisticsPoint_01:3|granary_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:3|citizenCenter_01:2|logisticsHub_01:3|shop_01:2|workshop_01:2|dock_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_02:3|windVane_01:3|citizenCenter_01:2|logisticsHub_01:2|sail_01:2|potentialTower_01:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:2|residence_03:2|windVane_01:3|citizenCenter_01:3|logisticsHub_01:3|dock_01:2</x:t>
   </x:si>
   <x:si>
     <x:t>stageId</x:t>
@@ -583,7 +715,7 @@
     <x:t>mapWidth</x:t>
   </x:si>
   <x:si>
-    <x:t>本关地图宽（格；需求=250）</x:t>
+    <x:t>本关地图宽（格；需求=250。地图稀疏存储，岛屿只占其中一部分，其余为虚空）</x:t>
   </x:si>
   <x:si>
     <x:t>mapHeight</x:t>
@@ -592,18 +724,33 @@
     <x:t>本关地图高（格；需求=250）</x:t>
   </x:si>
   <x:si>
-    <x:t>关卡岛屿模型/场景资源路径（Resources 相对路径或 Addressables key，与 BuildingVariant.prefabPath 同口径；空=白模占位）</x:t>
+    <x:t>关卡岛屿模型/场景资源路径（Resources 相对路径或 Addressables key，与 BuildingVariant.prefabPath 同口径；空=白模占位）。由菜单 Tools/美术/生成白模 Prefab 生成到 Assets/Resources/Prefab/Stage/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>islandCellSpan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>岛屿模型入场时缩放到的可玩跨度（格）：把模型 XZ 包围盒的长边等比缩放到 islandCellSpan × GameConfig.cellSize 米，居中放在地图中心。地形刷子按缩放后的岛面轮廓描摹地块</x:t>
   </x:si>
   <x:si>
     <x:t>浮空岛·一</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Stage/stage_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>浮空岛·二</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Stage/stage_02</x:t>
+  </x:si>
+  <x:si>
     <x:t>浮空岛·三</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefab/Stage/stage_03</x:t>
+  </x:si>
+  <x:si>
     <x:t>key</x:t>
   </x:si>
   <x:si>
@@ -662,6 +809,12 @@
   </x:si>
   <x:si>
     <x:t>巨型风车通用加分——范围内任意普通建筑获得；有专属条目（BuildingMapElement.exclusive=TRUE）的建筑用专属分替代不叠加（§6；0=待定）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>layerHeightFactor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>层高折算系数 k（决策 26）：建筑/元素的影响范围为球形，三维欧氏距离 = √(水平格距² + (高度层差×k)²)。表现层的 EGB verticalGridHeight = k × cellSize，两边必须同一个 k（当前预制体 2/2 → k=1）</x:t>
   </x:si>
   <x:si>
     <x:t>anchorDockDecayPercents</x:t>
@@ -1103,8 +1256,8 @@
     <x:col min="2" max="2" width="8.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="101.282054" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="93.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="43.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="72.282054" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.282054" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="177.710625" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="55.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="64.282054" style="0" customWidth="1"/>
@@ -1251,10 +1404,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>36</x:v>
@@ -1283,10 +1436,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>36</x:v>
@@ -1312,10 +1465,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>36</x:v>
@@ -1341,10 +1494,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>46</x:v>
@@ -1376,7 +1529,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>50</x:v>
@@ -1405,10 +1558,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>56</x:v>
@@ -1437,10 +1590,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>36</x:v>
@@ -1466,10 +1619,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>62</x:v>
@@ -1481,7 +1634,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="L11" s="0">
-        <x:v>0</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="M11" s="0">
         <x:v>1</x:v>
@@ -1501,10 +1654,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>36</x:v>
@@ -1530,10 +1683,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
         <x:v>36</x:v>
@@ -1559,10 +1712,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>36</x:v>
@@ -1588,10 +1741,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>75</x:v>
@@ -1620,16 +1773,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="L16" s="0">
         <x:v>0</x:v>
@@ -1640,25 +1793,25 @@
     </x:row>
     <x:row r="17" spans="1:13">
       <x:c r="A17" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>50</x:v>
@@ -1672,22 +1825,22 @@
     </x:row>
     <x:row r="18" spans="1:13">
       <x:c r="A18" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>50</x:v>
@@ -1724,63 +1877,63 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
@@ -1789,21 +1942,21 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1826,21 +1979,21 @@
     <x:col min="1" max="1" width="34.567768" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="57.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="118.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="60.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="145.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1859,254 +2012,254 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2126,9 +2279,9 @@
   <x:dimension ref="A1:C18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="89.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="122.996339" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="67.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="74.424911" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="100.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="41.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -2136,10 +2289,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -2155,13 +2308,13 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -2169,10 +2322,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -2180,10 +2333,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -2191,10 +2344,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -2202,10 +2355,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -2213,10 +2366,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -2224,10 +2377,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -2235,10 +2388,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -2246,10 +2399,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -2257,10 +2410,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -2268,10 +2421,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -2279,10 +2432,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -2290,10 +2443,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -2301,32 +2454,32 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2343,38 +2496,46 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F10"/>
+  <x:dimension ref="A1:H10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="64.567768" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="62.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="8.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="118.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="51.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="46.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="48.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="47.853482" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="44.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="76.139196" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="141.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:8">
       <x:c r="A1" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>145</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8">
       <x:c r="A2" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -2393,39 +2554,51 @@
       <x:c r="F2" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
+      <x:c r="G2" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8">
       <x:c r="A3" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H3" s="1" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8">
       <x:c r="A4" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>1</x:v>
@@ -2433,56 +2606,74 @@
       <x:c r="F4" s="0">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
+      <x:c r="G4" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
       <x:c r="A5" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8">
       <x:c r="A6" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
       <x:c r="A7" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>0</x:v>
@@ -2493,36 +2684,48 @@
       <x:c r="F7" s="0">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6">
+      <x:c r="G7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8">
       <x:c r="A8" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:6">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8">
       <x:c r="A9" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D9" s="0">
         <x:v>0</x:v>
@@ -2533,16 +2736,22 @@
       <x:c r="F9" s="0">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:6">
+      <x:c r="G9" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8">
       <x:c r="A10" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D10" s="0">
         <x:v>0</x:v>
@@ -2552,6 +2761,12 @@
       </x:c>
       <x:c r="F10" s="0">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>97</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2578,13 +2793,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -2595,18 +2810,18 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -2614,7 +2829,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>0</x:v>
@@ -2625,10 +2840,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -2636,10 +2851,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>1.2</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -2647,10 +2862,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0</x:v>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -2658,10 +2873,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0</x:v>
+        <x:v>1.8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -2669,10 +2884,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>0</x:v>
+        <x:v>2.2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2693,30 +2908,30 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16.567768" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="36.567768" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31.282054" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="22.710625" style="0" customWidth="1"/>
     <x:col min="4" max="5" width="21.853482" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="116.139196" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="168.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
@@ -2741,22 +2956,22 @@
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -2775,13 +2990,16 @@
       <x:c r="E4" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>2</x:v>
@@ -2791,6 +3009,9 @@
       </x:c>
       <x:c r="E5" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -2798,7 +3019,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>0</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>2</x:v>
@@ -2808,6 +3029,9 @@
       </x:c>
       <x:c r="E6" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -2815,7 +3039,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>0</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>2</x:v>
@@ -2825,6 +3049,9 @@
       </x:c>
       <x:c r="E7" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -2832,7 +3059,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>0</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>2</x:v>
@@ -2842,6 +3069,9 @@
       </x:c>
       <x:c r="E8" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -2849,7 +3079,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>0</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>2</x:v>
@@ -2859,6 +3089,9 @@
       </x:c>
       <x:c r="E9" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -2866,7 +3099,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>0</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>2</x:v>
@@ -2876,6 +3109,9 @@
       </x:c>
       <x:c r="E10" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -2883,7 +3119,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>0</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>2</x:v>
@@ -2893,6 +3129,9 @@
       </x:c>
       <x:c r="E11" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -2900,7 +3139,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>0</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>2</x:v>
@@ -2910,6 +3149,9 @@
       </x:c>
       <x:c r="E12" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -2917,7 +3159,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>0</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>2</x:v>
@@ -2927,6 +3169,9 @@
       </x:c>
       <x:c r="E13" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
@@ -2934,7 +3179,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>0</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>2</x:v>
@@ -2944,6 +3189,9 @@
       </x:c>
       <x:c r="E14" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -2951,7 +3199,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>0</x:v>
+        <x:v>1010</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>2</x:v>
@@ -2961,6 +3209,9 @@
       </x:c>
       <x:c r="E15" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -2968,7 +3219,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>0</x:v>
+        <x:v>1160</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>2</x:v>
@@ -2978,6 +3229,9 @@
       </x:c>
       <x:c r="E16" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -2985,7 +3239,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>0</x:v>
+        <x:v>1320</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>2</x:v>
@@ -2995,6 +3249,9 @@
       </x:c>
       <x:c r="E17" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -3002,7 +3259,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>0</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>2</x:v>
@@ -3012,6 +3269,9 @@
       </x:c>
       <x:c r="E18" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
@@ -3019,7 +3279,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>0</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>2</x:v>
@@ -3029,6 +3289,9 @@
       </x:c>
       <x:c r="E19" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
@@ -3036,7 +3299,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>0</x:v>
+        <x:v>1860</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>2</x:v>
@@ -3046,6 +3309,9 @@
       </x:c>
       <x:c r="E20" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -3053,7 +3319,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>0</x:v>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>2</x:v>
@@ -3063,6 +3329,9 @@
       </x:c>
       <x:c r="E21" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -3070,7 +3339,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>0</x:v>
+        <x:v>2270</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>2</x:v>
@@ -3080,6 +3349,9 @@
       </x:c>
       <x:c r="E22" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -3087,7 +3359,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>0</x:v>
+        <x:v>2490</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>2</x:v>
@@ -3097,6 +3369,9 @@
       </x:c>
       <x:c r="E23" s="0">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>225</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3113,33 +3388,38 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E6"/>
+  <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="8.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="4" width="16.567768" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="85.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="143.567768" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="102.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5">
+    <x:row r="1" spans="1:6">
       <x:c r="A1" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6">
       <x:c r="A2" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
@@ -3155,30 +3435,36 @@
       <x:c r="E2" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5">
+      <x:c r="F2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6">
       <x:c r="A3" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>189</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:6">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>250</x:v>
@@ -3187,15 +3473,18 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F4" s="0">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:6">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>250</x:v>
@@ -3204,15 +3493,18 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F5" s="0">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:6">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>250</x:v>
@@ -3221,7 +3513,10 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3238,46 +3533,46 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D10"/>
+  <x:dimension ref="A1:D11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="25.139196" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="5.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="88.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="121.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
@@ -3286,105 +3581,119 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>215</x:v>
+      <x:c r="C11" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>266</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3412,21 +3721,21 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>10</x:v>
@@ -3435,63 +3744,63 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -3019,7 +3019,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>110</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>2</x:v>
@@ -3039,7 +3039,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>170</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>2</x:v>
@@ -3059,7 +3059,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>240</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>2</x:v>
@@ -3079,7 +3079,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>320</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>2</x:v>
@@ -3099,7 +3099,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>410</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>2</x:v>
@@ -3119,7 +3119,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>510</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>2</x:v>
@@ -3139,7 +3139,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>620</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>2</x:v>
@@ -3159,7 +3159,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>740</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>2</x:v>
@@ -3179,7 +3179,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>870</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>2</x:v>
@@ -3199,7 +3199,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1010</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>2</x:v>
@@ -3219,7 +3219,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1160</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>2</x:v>
@@ -3239,7 +3239,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1320</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>2</x:v>
@@ -3259,7 +3259,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1490</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>2</x:v>
@@ -3279,7 +3279,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>1670</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>2</x:v>
@@ -3299,7 +3299,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1860</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>2</x:v>
@@ -3319,7 +3319,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>2060</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>2</x:v>
@@ -3339,7 +3339,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>2270</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>2</x:v>
@@ -3359,7 +3359,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>2490</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>2</x:v>

--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -289,6 +289,9 @@
     <x:t>所属建筑模板 Id → Building 表（一个模板可挂多个变体；计分/关系/建造限制走模板，占地与外观走变体）</x:t>
   </x:si>
   <x:si>
+    <x:t>变体显示名（UI 手牌用）。空=沿用 Building.nameCn；一个模板挂多个变体时必须逐个填，否则玩家在手牌里分不出 2×2 居民区和 L 形居民区</x:t>
+  </x:si>
+  <x:si>
     <x:t>footprint</x:t>
   </x:si>
   <x:si>
@@ -394,12 +397,18 @@
     <x:t>residence_01</x:t>
   </x:si>
   <x:si>
+    <x:t>居民区·方形</x:t>
+  </x:si>
+  <x:si>
     <x:t>Prefab/Building/residence_01</x:t>
   </x:si>
   <x:si>
     <x:t>residence_02</x:t>
   </x:si>
   <x:si>
+    <x:t>居民区·L形</x:t>
+  </x:si>
+  <x:si>
     <x:t>###|#..</x:t>
   </x:si>
   <x:si>
@@ -407,6 +416,9 @@
   </x:si>
   <x:si>
     <x:t>residence_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>居民区·凹形</x:t>
   </x:si>
   <x:si>
     <x:t>#.#|###</x:t>
@@ -1877,21 +1889,21 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>10</x:v>
@@ -1900,12 +1912,12 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
@@ -1914,12 +1926,12 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>10</x:v>
@@ -1928,12 +1940,12 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
@@ -1942,12 +1954,12 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
@@ -1956,7 +1968,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1973,16 +1985,17 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D20"/>
+  <x:dimension ref="A1:E20"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34.567768" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="57.996339" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="118.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="145.567768" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="79.139196" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="118.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="145.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4">
+    <x:row r="1" spans="1:5">
       <x:c r="A1" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
@@ -1990,13 +2003,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -2004,13 +2020,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="E2" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:4">
+    <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
@@ -2018,248 +2037,260 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
+      <x:c r="E4" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:4">
+      <x:c r="E5" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:4">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:4">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
+      <x:c r="E9" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4">
+      <x:c r="E10" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:5">
       <x:c r="A11" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:4">
+      <x:c r="E11" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:5">
       <x:c r="A12" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:4">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:4">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:4">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:5">
       <x:c r="A15" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:4">
+      <x:c r="E15" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:5">
       <x:c r="A16" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:4">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:5">
       <x:c r="A17" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:4">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:5">
       <x:c r="A18" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:4">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:5">
       <x:c r="A19" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:4">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:5">
       <x:c r="A20" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>137</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2289,10 +2320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -2308,13 +2339,13 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -2322,10 +2353,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -2333,10 +2364,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -2344,10 +2375,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -2355,10 +2386,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -2366,10 +2397,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -2377,10 +2408,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -2388,10 +2419,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
@@ -2399,10 +2430,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
@@ -2410,10 +2441,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -2421,10 +2452,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -2432,10 +2463,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
@@ -2443,10 +2474,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -2454,10 +2485,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -2465,10 +2496,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
@@ -2476,10 +2507,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2511,28 +2542,28 @@
   <x:sheetData>
     <x:row r="1" spans="1:8">
       <x:c r="A1" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
@@ -2563,39 +2594,39 @@
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
       <x:c r="A4" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D4" s="0">
         <x:v>12</x:v>
@@ -2610,18 +2641,18 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
       <x:c r="A5" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>8</x:v>
@@ -2636,18 +2667,18 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
       <x:c r="A6" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>6</x:v>
@@ -2662,7 +2693,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
@@ -2670,10 +2701,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>0</x:v>
@@ -2688,18 +2719,18 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
       <x:c r="A8" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>0</x:v>
@@ -2714,18 +2745,18 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:8">
       <x:c r="A9" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D9" s="0">
         <x:v>0</x:v>
@@ -2740,7 +2771,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
@@ -2748,10 +2779,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D10" s="0">
         <x:v>0</x:v>
@@ -2766,7 +2797,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2793,13 +2824,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -2810,18 +2841,18 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -2829,7 +2860,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>0</x:v>
@@ -2840,7 +2871,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>1</x:v>
@@ -2851,7 +2882,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>1.2</x:v>
@@ -2862,7 +2893,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>1.5</x:v>
@@ -2873,7 +2904,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>1.8</x:v>
@@ -2884,7 +2915,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>2.2</x:v>
@@ -2916,22 +2947,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
@@ -2956,22 +2987,22 @@
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -2991,7 +3022,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -3011,7 +3042,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -3031,7 +3062,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -3051,7 +3082,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -3071,7 +3102,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -3091,7 +3122,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -3111,7 +3142,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -3131,7 +3162,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -3151,7 +3182,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -3171,7 +3202,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
@@ -3191,7 +3222,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -3211,7 +3242,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -3231,7 +3262,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -3251,7 +3282,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -3271,7 +3302,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
@@ -3291,7 +3322,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
@@ -3311,7 +3342,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -3331,7 +3362,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -3351,7 +3382,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -3371,7 +3402,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3401,22 +3432,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
@@ -3441,22 +3472,22 @@
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -3464,7 +3495,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>250</x:v>
@@ -3473,7 +3504,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F4" s="0">
         <x:v>40</x:v>
@@ -3484,7 +3515,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>250</x:v>
@@ -3493,7 +3524,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>40</x:v>
@@ -3504,7 +3535,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>250</x:v>
@@ -3513,7 +3544,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="F6" s="0">
         <x:v>40</x:v>
@@ -3544,35 +3575,35 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
@@ -3581,26 +3612,26 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
@@ -3609,12 +3640,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
@@ -3623,12 +3654,12 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>259</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>10</x:v>
@@ -3637,12 +3668,12 @@
         <x:v>-20</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>18</x:v>
@@ -3651,12 +3682,12 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>10</x:v>
@@ -3665,35 +3696,35 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3721,21 +3752,21 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>10</x:v>
@@ -3744,12 +3775,12 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
@@ -3758,12 +3789,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>10</x:v>
@@ -3772,12 +3803,12 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
@@ -3786,12 +3817,12 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>10</x:v>
@@ -3800,7 +3831,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -174,6 +174,9 @@
   </x:si>
   <x:si>
     <x:t>物流点经物流风互联的一次性加分（每对物流点仅计一次，链式相邻配对；本次风系统实装新增）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0|5|10|18|28|40</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -912,6 +915,9 @@
           <x:t>TRUE</x:t>
         </x:is>
       </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="L5" s="0">
         <x:v>0</x:v>
       </x:c>

--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -12,7 +12,7 @@
     <x:sheet name="MapElement" sheetId="4" r:id="rId4"/>
     <x:sheet name="WindLevel" sheetId="5" r:id="rId5"/>
     <x:sheet name="Level" sheetId="6" r:id="rId6"/>
-    <x:sheet name="BuildingGroupTheme" sheetId="12" r:id="rId15"/>
+    <x:sheet name="BuildingGroupTheme" sheetId="14" r:id="rId15"/>
     <x:sheet name="Stage" sheetId="7" r:id="rId7"/>
     <x:sheet name="GameConfig" sheetId="8" r:id="rId8"/>
     <x:sheet name="WindConfig" sheetId="9" r:id="rId9"/>
@@ -26,6 +26,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>0|5|10|18|28|40</x:t>
+  </x:si>
+  <x:si>
     <x:t>themes</x:t>
   </x:si>
   <x:si>
@@ -35,148 +38,154 @@
     <x:t>本级强制使用的建筑组主题（主题Id → BuildingGroupTheme 表主键，多个用|分隔）。留空 = 按 BuildingGroupTheme 的 minLevel/maxLevel 自动筛选本级可用主题，这是常规做法；只有需要写死开局体验时才填</x:t>
   </x:si>
   <x:si>
+    <x:t>civicCenter|mining</x:t>
+  </x:si>
+  <x:si>
     <x:t>mining|farmland</x:t>
   </x:si>
   <x:si>
+    <x:t>windVane_01:2:1:2|residence_01:5:2:3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>风向标社区</x:t>
+  </x:si>
+  <x:si>
+    <x:t>windVaneQuarter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dock_01:2:1:1|workshop_01:3:1:2|logisticsPoint_01:4:1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>港口船坞</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harbor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>logisticsPoint_01:6:2:3|logisticsHub_01:2:1:1|workshop_01:2:0:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>物流网络</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>logisticsNet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>potentialTower_01:4:1:2|windmill_01:2:1:1|sail_01:3:1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>风能塔群</x:t>
+  </x:si>
+  <x:si>
+    <x:t>windPower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>citizenCenter_01:1:1:1|residence_01:5:1:3|residence_03:3:0:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>市民中心区</x:t>
+  </x:si>
+  <x:si>
+    <x:t>civicCenter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:4:1:2|restaurant_01:3:1:2|shop_01:3:1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>商业街</x:t>
+  </x:si>
+  <x:si>
+    <x:t>commerceStreet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residence_01:5:2:3|residence_02:3:0:2|residence_03:3:0:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>居民街区</x:t>
+  </x:si>
+  <x:si>
+    <x:t>residentialBlock</x:t>
+  </x:si>
+  <x:si>
+    <x:t>farm_01:5:2:3|granary_01:3:1:2|windmill_01:1:0:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>粮储基地</x:t>
+  </x:si>
+  <x:si>
+    <x:t>granaryDepot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>farm_01:6:2:4|windmill_01:2:0:1|sail_01:2:0:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>农田耕作</x:t>
+  </x:si>
+  <x:si>
+    <x:t>farmland</x:t>
+  </x:si>
+  <x:si>
+    <x:t>miningStation_01:6:2:3|workshop_01:2:1:1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>矿业开采</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mining</x:t>
+  </x:si>
+  <x:si>
+    <x:t>成员配方：变体Id:权重[:最少[:最多]]，多条用|分隔。权重=剩余名额里的抽取权重（核心建筑权重高=出得多），最少=本组保底几栋（默认 0），最多=本组上限（默认 0 = 不限）。例 miningStation_01:6:2:3|workshop_01:2:1:1 = 采矿站 2~3 栋、工坊恰好 1 栋</x:t>
+  </x:si>
+  <x:si>
+    <x:t>members</x:t>
+  </x:si>
+  <x:si>
+    <x:t>本主题一局最多被玩家选中几次，选满后不再进候选池；0 = 不限。用来给地标建筑封顶——市民中心配 1:1:1 且本列填 3，一局就最多 3 个市民中心</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maxPerRun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>同一等级内被抽中的权重（正整数）。同一级的两组必定是两个不同主题，抽中后不放回</x:t>
+  </x:si>
+  <x:si>
+    <x:t>weight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>最晚出现等级（含）。0 = 一直可用</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maxLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>最早出现等级（含）。主题按阶段解锁：前期生产（矿业/农业）→ 中期居住商业 → 后期物流港口</x:t>
+  </x:si>
+  <x:si>
+    <x:t>minLevel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>显示名（手牌选组按钮上会显示，让玩家一眼看懂这组是干什么的）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nameCn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>主题 Id（主键，camelCase）。一个主题 = 一组「互相加分」的建筑配方，选组时一组只出一个主题的建筑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
     <x:t>themeId</x:t>
   </x:si>
   <x:si>
-    <x:t>nameCn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>minLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maxLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>weight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>members</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>主题 Id（主键，camelCase）。一个主题 = 一组「互相加分」的建筑配方，选组时一组只出一个主题的建筑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>显示名（手牌选组按钮上会显示，让玩家一眼看懂这组是干什么的）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>最早出现等级（含）。主题按阶段解锁：前期生产（矿业/农业）→ 中期居住商业 → 后期物流港口</x:t>
-  </x:si>
-  <x:si>
-    <x:t>最晚出现等级（含）。0 = 一直可用</x:t>
-  </x:si>
-  <x:si>
-    <x:t>同一等级内被抽中的权重（正整数）。同一级的两组必定是两个不同主题，抽中后不放回</x:t>
-  </x:si>
-  <x:si>
-    <x:t>成员配方：变体Id:权重[:最少[:最多]]，多条用|分隔。权重=剩余名额里的抽取权重（核心建筑权重高=出得多），最少=本组保底几栋（默认 0），最多=本组上限（默认 0 = 不限）。例 miningStation_01:6:2:3|workshop_01:2:1:1 = 采矿站 2~3 栋、工坊恰好 1 栋</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mining</x:t>
-  </x:si>
-  <x:si>
-    <x:t>矿业开采</x:t>
-  </x:si>
-  <x:si>
-    <x:t>miningStation_01:6:2:3|workshop_01:2:1:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>farmland</x:t>
-  </x:si>
-  <x:si>
-    <x:t>农田风车</x:t>
-  </x:si>
-  <x:si>
-    <x:t>farm_01:6:2:4|windmill_01:2:1:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>granaryDepot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>粮储基地</x:t>
-  </x:si>
-  <x:si>
-    <x:t>farm_01:5:2:3|granary_01:3:1:2|windmill_01:2:0:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>residentialBlock</x:t>
-  </x:si>
-  <x:si>
-    <x:t>居民街区</x:t>
-  </x:si>
-  <x:si>
-    <x:t>residence_01:5:2:3|residence_02:3:0:2|residence_03:3:0:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>commerceStreet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>商业街</x:t>
-  </x:si>
-  <x:si>
-    <x:t>residence_01:4:1:2|restaurant_01:3:1:2|shop_01:3:1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>civicCenter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>市民中心区</x:t>
-  </x:si>
-  <x:si>
-    <x:t>citizenCenter_01:1:1:1|residence_01:5:1:3|residence_03:3:0:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windPower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>风能塔群</x:t>
-  </x:si>
-  <x:si>
-    <x:t>potentialTower_01:4:1:2|windmill_01:4:1:2|sail_01:2:0:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>logisticsNet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>物流网络</x:t>
-  </x:si>
-  <x:si>
-    <x:t>logisticsPoint_01:6:2:3|logisticsHub_01:2:1:1|workshop_01:2:0:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harbor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>港口船坞</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dock_01:2:1:1|workshop_01:3:1:2|logisticsPoint_01:4:1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windVaneQuarter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>风向标社区</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windVane_01:2:1:2|residence_01:5:2:3</x:t>
-  </x:si>
-  <x:si>
     <x:t>windLinkScore</x:t>
   </x:si>
   <x:si>
     <x:t>物流点经物流风互联的一次性加分（每对物流点仅计一次，链式相邻配对；本次风系统实装新增）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0|5|10|18|28|40</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -916,7 +925,7 @@
         </x:is>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L5" s="0">
         <x:v>0</x:v>
@@ -1620,16 +1629,16 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1646,82 +1655,92 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F13"/>
+  <x:dimension ref="A1:G13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="56.853482" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="32.710625" style="0" customWidth="1"/>
     <x:col min="3" max="4" width="10.710625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="41.996339" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="60.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="60.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>1</x:v>
@@ -1732,16 +1751,19 @@
       <x:c r="E4" s="0">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
+      <x:c r="F4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>1</x:v>
@@ -1752,16 +1774,19 @@
       <x:c r="E5" s="0">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
+      <x:c r="F5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>3</x:v>
@@ -1772,16 +1797,19 @@
       <x:c r="E6" s="0">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6">
+      <x:c r="F6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>6</x:v>
@@ -1792,16 +1820,19 @@
       <x:c r="E7" s="0">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6">
+      <x:c r="F7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>8</x:v>
@@ -1812,19 +1843,22 @@
       <x:c r="E8" s="0">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:6">
+      <x:c r="F8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="0">
         <x:v>20</x:v>
@@ -1832,16 +1866,19 @@
       <x:c r="E9" s="0">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:6">
+      <x:c r="F9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>11</x:v>
@@ -1852,16 +1889,19 @@
       <x:c r="E10" s="0">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:6">
+      <x:c r="F10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>12</x:v>
@@ -1872,16 +1912,19 @@
       <x:c r="E11" s="0">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:6">
+      <x:c r="F11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>13</x:v>
@@ -1892,16 +1935,19 @@
       <x:c r="E12" s="0">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:6">
+      <x:c r="F12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>15</x:v>
@@ -1912,8 +1958,11 @@
       <x:c r="E13" s="0">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>47</x:v>
+      <x:c r="F13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3275,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
@@ -3305,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -3335,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -3355,7 +3404,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -3374,13 +3423,16 @@
       <x:c r="E5" s="0">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>85</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>2</x:v>
@@ -3397,7 +3449,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>110</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>2</x:v>
@@ -3414,7 +3466,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>130</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>2</x:v>
@@ -3431,7 +3483,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>150</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>2</x:v>
@@ -3482,7 +3534,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>210</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>2</x:v>
@@ -3499,7 +3551,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>225</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>2</x:v>
@@ -3516,7 +3568,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>245</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>2</x:v>
@@ -3533,7 +3585,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>260</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>2</x:v>
@@ -3550,7 +3602,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>275</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>2</x:v>
@@ -3567,7 +3619,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>290</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>2</x:v>
@@ -3584,7 +3636,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>305</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>2</x:v>
@@ -3652,7 +3704,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>360</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>2</x:v>

--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -12,11 +12,11 @@
     <x:sheet name="MapElement" sheetId="4" r:id="rId4"/>
     <x:sheet name="WindLevel" sheetId="5" r:id="rId5"/>
     <x:sheet name="Level" sheetId="6" r:id="rId6"/>
-    <x:sheet name="BuildingGroupTheme" sheetId="14" r:id="rId15"/>
-    <x:sheet name="Stage" sheetId="7" r:id="rId7"/>
-    <x:sheet name="GameConfig" sheetId="8" r:id="rId8"/>
-    <x:sheet name="WindConfig" sheetId="9" r:id="rId9"/>
-    <x:sheet name="LogisticsConfig" sheetId="10" r:id="rId10"/>
+    <x:sheet name="BuildingGroupTheme" sheetId="7" r:id="rId7"/>
+    <x:sheet name="Stage" sheetId="8" r:id="rId8"/>
+    <x:sheet name="GameConfig" sheetId="9" r:id="rId9"/>
+    <x:sheet name="WindConfig" sheetId="10" r:id="rId10"/>
+    <x:sheet name="LogisticsConfig" sheetId="11" r:id="rId11"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725" fullCalcOnLoad="1"/>
@@ -26,166 +26,43 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>0|5|10|18|28|40</x:t>
+    <x:t>residence:10|granary:12</x:t>
   </x:si>
   <x:si>
-    <x:t>themes</x:t>
+    <x:t>restaurant:16:2|shop:16:2|citizenCenter:20:1|residence:8:4|logisticsPoint:10:2|logisticsHub:15:1</x:t>
   </x:si>
   <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>本级强制使用的建筑组主题（主题Id → BuildingGroupTheme 表主键，多个用|分隔）。留空 = 按 BuildingGroupTheme 的 minLevel/maxLevel 自动筛选本级可用主题，这是常规做法；只有需要写死开局体验时才填</x:t>
-  </x:si>
-  <x:si>
-    <x:t>civicCenter|mining</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mining|farmland</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windVane_01:2:1:2|residence_01:5:2:3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>风向标社区</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windVaneQuarter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dock_01:2:1:1|workshop_01:3:1:2|logisticsPoint_01:4:1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>港口船坞</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harbor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>logisticsPoint_01:6:2:3|logisticsHub_01:2:1:1|workshop_01:2:0:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>物流网络</x:t>
+    <x:t>unlockScore</x:t>
   </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>logisticsNet</x:t>
+    <x:t>解锁本组所需的累计分门槛（相对本关基线的增量；第 1 组=0 免费）。判定是「本关已得分 ≥ 本值 × Stage.unlockScoreMult」——达标即可解锁，**不扣分**。跨关时分数保留，门槛按进入本关时的总分重新起算（§4.1）</x:t>
   </x:si>
   <x:si>
-    <x:t>potentialTower_01:4:1:2|windmill_01:2:1:1|sail_01:3:1:2</x:t>
+    <x:t>residence_01:6:2:3|restaurant_01:2:1:1|shop_01:2:1:1</x:t>
   </x:si>
   <x:si>
-    <x:t>风能塔群</x:t>
+    <x:t>groupCount</x:t>
   </x:si>
   <x:si>
-    <x:t>windPower</x:t>
+    <x:t>clearScore</x:t>
   </x:si>
   <x:si>
-    <x:t>citizenCenter_01:1:1:1|residence_01:5:1:3|residence_03:3:0:2</x:t>
+    <x:t>unlockScoreMult</x:t>
   </x:si>
   <x:si>
-    <x:t>市民中心区</x:t>
+    <x:t>float</x:t>
   </x:si>
   <x:si>
-    <x:t>civicCenter</x:t>
+    <x:t>本关提供几组建筑（用 Level 表的前 N 行）。按本关地图容得下多少建筑定——地块摆满后每组收益会转负，组数超过产能只是让玩家白扣分。组数用完且已达通关分即可进下一关</x:t>
   </x:si>
   <x:si>
-    <x:t>residence_01:4:1:2|restaurant_01:3:1:2|shop_01:3:1:2</x:t>
+    <x:t>通关本关所需的累计分门槛（相对本关基线的增量）。**按「大约打到六成组数时达标」定**——解锁下一关只看这个分，不要求把本关的组建完。达标后「进入下一关」随时可点，但**不强制**：玩家可以继续摆到组数用完或分数不够解锁下一组，把分数刷高了带进下一关</x:t>
   </x:si>
   <x:si>
-    <x:t>商业街</x:t>
-  </x:si>
-  <x:si>
-    <x:t>commerceStreet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>residence_01:5:2:3|residence_02:3:0:2|residence_03:3:0:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>居民街区</x:t>
-  </x:si>
-  <x:si>
-    <x:t>residentialBlock</x:t>
-  </x:si>
-  <x:si>
-    <x:t>farm_01:5:2:3|granary_01:3:1:2|windmill_01:1:0:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>粮储基地</x:t>
-  </x:si>
-  <x:si>
-    <x:t>granaryDepot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>farm_01:6:2:4|windmill_01:2:0:1|sail_01:2:0:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>农田耕作</x:t>
-  </x:si>
-  <x:si>
-    <x:t>farmland</x:t>
-  </x:si>
-  <x:si>
-    <x:t>miningStation_01:6:2:3|workshop_01:2:1:1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>矿业开采</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mining</x:t>
-  </x:si>
-  <x:si>
-    <x:t>成员配方：变体Id:权重[:最少[:最多]]，多条用|分隔。权重=剩余名额里的抽取权重（核心建筑权重高=出得多），最少=本组保底几栋（默认 0），最多=本组上限（默认 0 = 不限）。例 miningStation_01:6:2:3|workshop_01:2:1:1 = 采矿站 2~3 栋、工坊恰好 1 栋</x:t>
-  </x:si>
-  <x:si>
-    <x:t>members</x:t>
-  </x:si>
-  <x:si>
-    <x:t>本主题一局最多被玩家选中几次，选满后不再进候选池；0 = 不限。用来给地标建筑封顶——市民中心配 1:1:1 且本列填 3，一局就最多 3 个市民中心</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maxPerRun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>同一等级内被抽中的权重（正整数）。同一级的两组必定是两个不同主题，抽中后不放回</x:t>
-  </x:si>
-  <x:si>
-    <x:t>weight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>最晚出现等级（含）。0 = 一直可用</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maxLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>最早出现等级（含）。主题按阶段解锁：前期生产（矿业/农业）→ 中期居住商业 → 后期物流港口</x:t>
-  </x:si>
-  <x:si>
-    <x:t>minLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>显示名（手牌选组按钮上会显示，让玩家一眼看懂这组是干什么的）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nameCn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>主题 Id（主键，camelCase）。一个主题 = 一组「互相加分」的建筑配方，选组时一组只出一个主题的建筑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>themeId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>windLinkScore</x:t>
-  </x:si>
-  <x:si>
-    <x:t>物流点经物流风互联的一次性加分（每对物流点仅计一次，链式相邻配对；本次风系统实装新增）</x:t>
+    <x:t>本关对 Level.unlockScore 的整体倍率。Level 表那条门槛曲线是按第 1 关的产能标定的，别的关地图不一样、产能也不一样，用这个倍率把同一条曲线缩放到本关的量级；1 = 直接用原曲线</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -261,9 +138,8 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="0" pivotButton="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="0" pivotButton="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -924,8 +800,10 @@
           <x:t>TRUE</x:t>
         </x:is>
       </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>0</x:v>
+      <x:c r="I5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>0|5|10|18|28|40</x:t>
+        </x:is>
       </x:c>
       <x:c r="L5" s="0">
         <x:v>0</x:v>
@@ -1499,10 +1377,10 @@
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20.567768" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="4.853482" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="5.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="56.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="74.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -1530,7 +1408,7 @@
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="inlineStr">
         <x:is>
-          <x:t>coverRadius</x:t>
+          <x:t>maxWindLevel</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" s="0" t="inlineStr">
@@ -1543,14 +1421,14 @@
       </x:c>
       <x:c r="D2" s="0" t="inlineStr">
         <x:is>
-          <x:t>物流点本地覆盖半径（格，§10.3；范围内常规建筑获得已接入物流状态；0=待定）</x:t>
+          <x:t>风力等级上限（合并后不超过此级，§8.5=5）</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="inlineStr">
         <x:is>
-          <x:t>baseCoverScore</x:t>
+          <x:t>initialWindLevelMin</x:t>
         </x:is>
       </x:c>
       <x:c r="B3" s="0" t="inlineStr">
@@ -1559,18 +1437,18 @@
         </x:is>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="0" t="inlineStr">
         <x:is>
-          <x:t>基础物流覆盖分（每建筑仅计一次，本地覆盖与物流风覆盖同状态不叠加 §10.3/10.4；0=待定）</x:t>
+          <x:t>初始风强度随机下限（1~5；§20 待定）</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="inlineStr">
         <x:is>
-          <x:t>windExtendLength</x:t>
+          <x:t>initialWindLevelMax</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" s="0" t="inlineStr">
@@ -1583,14 +1461,14 @@
       </x:c>
       <x:c r="D4" s="0" t="inlineStr">
         <x:is>
-          <x:t>风经过物流点时延长的剩余长度（格，§10.5；0=待定）</x:t>
+          <x:t>初始风强度随机上限（1~5；§20 待定）</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="inlineStr">
         <x:is>
-          <x:t>windExtendMaxPerWind</x:t>
+          <x:t>initialWindLengthMin</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" s="0" t="inlineStr">
@@ -1599,18 +1477,18 @@
         </x:is>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="0" t="inlineStr">
         <x:is>
-          <x:t>同一股风最多获得的物流点延长次数（§10.5 已定=2；同点不重复延长为固定规则）</x:t>
+          <x:t>初始风传播长度随机下限（格；§20 待定。初始风数量在 MapElement.windSource 的 countMin/countMax）</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="inlineStr">
         <x:is>
-          <x:t>endgameScorePerCoveredBuilding</x:t>
+          <x:t>initialWindLengthMax</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="0" t="inlineStr">
@@ -1619,26 +1497,12 @@
         </x:is>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="0" t="inlineStr">
         <x:is>
-          <x:t>终局物流网络奖励：每个已接入物流的建筑在终局额外加分（只加分不给金币 §7.2；具体语义可再调整；0=待定）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
-      <x:c r="A7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>53</x:v>
+          <x:t>初始风传播长度随机上限（格；§20 待定）</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1650,319 +1514,161 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
+    <x:pageSetUpPr/>
   </x:sheetPr>
-  <x:dimension ref="A1:G13"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:dimension ref="A1:D7"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="56.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="4" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="41.996339" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="60.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="31.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="4.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="56.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
-      <x:c r="A1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7">
-      <x:c r="A2" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
+    <x:row r="1" spans="1:4">
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>key</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>value</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>desc</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="0" t="inlineStr">
+        <x:is>
+          <x:t>coverRadius</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="0" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="inlineStr">
+        <x:is>
+          <x:t>物流点本地覆盖半径（格，§10.3；范围内常规建筑获得已接入物流状态；0=待定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4">
+      <x:c r="A3" s="0" t="inlineStr">
+        <x:is>
+          <x:t>baseCoverScore</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="0" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="inlineStr">
+        <x:is>
+          <x:t>基础物流覆盖分（每建筑仅计一次，本地覆盖与物流风覆盖同状态不叠加 §10.3/10.4；0=待定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:4">
+      <x:c r="A4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>windExtendLength</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>风经过物流点时延长的剩余长度（格，§10.5；0=待定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:4">
+      <x:c r="A5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>windExtendMaxPerWind</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="0">
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="0">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E4" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="0">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E5" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
+      <x:c r="D5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>同一股风最多获得的物流点延长次数（§10.5 已定=2；同点不重复延长为固定规则）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>endgameScorePerCoveredBuilding</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>终局物流网络奖励：每个已接入物流的建筑在终局额外加分（只加分不给金币 §7.2；具体语义可再调整；0=待定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>windLinkScore</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="0">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="0">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E6" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F6" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E7" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
-      <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E8" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F8" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
-      <x:c r="A9" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E9" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
-      <x:c r="A10" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E10" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="0">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E11" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
-      <x:c r="A12" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E12" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:7">
-      <x:c r="A13" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D13" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E13" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>6</x:v>
+      <x:c r="D7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>物流点经物流风互联的一次性加分（每对物流点仅计一次，链式相邻配对；本次风系统实装新增）</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2658,10 +2364,8 @@
           <x:t>restaurant</x:t>
         </x:is>
       </x:c>
-      <x:c r="B13" s="0" t="inlineStr">
-        <x:is>
-          <x:t>residence:10</x:t>
-        </x:is>
+      <x:c r="B13" s="0" t="s">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -2694,10 +2398,8 @@
           <x:t>residence</x:t>
         </x:is>
       </x:c>
-      <x:c r="B16" s="0" t="inlineStr">
-        <x:is>
-          <x:t>restaurant:12:2|shop:12:2|citizenCenter:20:1|residence:8:4|logisticsPoint:10:2|logisticsHub:15:1</x:t>
-        </x:is>
+      <x:c r="B16" s="0" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="0" t="inlineStr">
         <x:is>
@@ -2864,7 +2566,7 @@
       </x:c>
       <x:c r="D3" s="1" t="inlineStr">
         <x:is>
-          <x:t>有效范围（格，自占地边缘起算；巨型风车加分范围 / 锚点有效范围 / 矿藏有效范围；地形类元素填 0）</x:t>
+          <x:t>有效范围（格，自占地边缘起算）。只用于摆放合法性（采矿站的 oreRange 必须在矿藏范围内），不参与计分：计分一律用结算建筑自身的 Building.radius。建议与对应建筑的 radius 保持一致，否则会出现“能建但吃不到分”的一圈位置。地形类元素填 0</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" s="1" t="inlineStr">
@@ -2977,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>3</x:v>
@@ -3047,10 +2749,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G8" s="0" t="inlineStr">
         <x:is>
@@ -3303,10 +3005,8 @@
           <x:t>level</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
-        <x:is>
-          <x:t>unlockCost</x:t>
-        </x:is>
+      <x:c r="B1" s="1" t="s">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="1" t="inlineStr">
         <x:is>
@@ -3323,8 +3023,10 @@
           <x:t>groupSizeMax</x:t>
         </x:is>
       </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>1</x:v>
+      <x:c r="F1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>themes</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
@@ -3333,28 +3035,28 @@
           <x:t>int</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="1" t="inlineStr">
+      <x:c r="B2" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="inlineStr">
         <x:is>
           <x:t>int</x:t>
         </x:is>
       </x:c>
-      <x:c r="C2" s="1" t="inlineStr">
+      <x:c r="D2" s="1" t="inlineStr">
         <x:is>
           <x:t>int</x:t>
         </x:is>
       </x:c>
-      <x:c r="D2" s="1" t="inlineStr">
+      <x:c r="E2" s="1" t="inlineStr">
         <x:is>
           <x:t>int</x:t>
         </x:is>
       </x:c>
-      <x:c r="E2" s="1" t="inlineStr">
-        <x:is>
-          <x:t>int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>2</x:v>
+      <x:c r="F2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>string[]</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -3363,10 +3065,8 @@
           <x:t>等级（主键 1~20，§4.1）</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="1" t="inlineStr">
-        <x:is>
-          <x:t>解锁本级费用（金币；第 1 级免费=0，随等级递增 §4.1）</x:t>
-        </x:is>
+      <x:c r="B3" s="1" t="s">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="1" t="inlineStr">
         <x:is>
@@ -3383,8 +3083,10 @@
           <x:t>每组建筑数量上限（设计建议 5，§4.2）</x:t>
         </x:is>
       </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>3</x:v>
+      <x:c r="F3" s="1" t="inlineStr">
+        <x:is>
+          <x:t>本级强制使用的建筑组主题（主题Id → BuildingGroupTheme 表主键，多个用|分隔）。留空 = 按 BuildingGroupTheme 的 minLevel/maxLevel 自动筛选本级可用主题，这是常规做法；只有需要写死开局体验时才填</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -3403,8 +3105,10 @@
       <x:c r="E4" s="0">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>5</x:v>
+      <x:c r="F4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>mining|farmland</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -3412,7 +3116,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>2</x:v>
@@ -3423,8 +3127,10 @@
       <x:c r="E5" s="0">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>4</x:v>
+      <x:c r="F5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>civicCenter|mining</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -3432,7 +3138,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>80</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>2</x:v>
@@ -3449,7 +3155,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>100</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>2</x:v>
@@ -3466,7 +3172,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>115</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>2</x:v>
@@ -3483,7 +3189,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>130</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>2</x:v>
@@ -3500,7 +3206,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>170</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>2</x:v>
@@ -3517,7 +3223,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>190</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>2</x:v>
@@ -3534,7 +3240,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>200</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>2</x:v>
@@ -3551,7 +3257,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>230</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>2</x:v>
@@ -3568,7 +3274,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>240</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>2</x:v>
@@ -3585,7 +3291,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>250</x:v>
+        <x:v>1700</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>2</x:v>
@@ -3602,7 +3308,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>265</x:v>
+        <x:v>1965</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>2</x:v>
@@ -3619,7 +3325,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>270</x:v>
+        <x:v>2360</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>2</x:v>
@@ -3636,7 +3342,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>280</x:v>
+        <x:v>2720</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>2</x:v>
@@ -3653,7 +3359,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>320</x:v>
+        <x:v>3115</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>2</x:v>
@@ -3670,7 +3376,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>330</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>2</x:v>
@@ -3687,7 +3393,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>345</x:v>
+        <x:v>3940</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>2</x:v>
@@ -3704,7 +3410,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>355</x:v>
+        <x:v>4290</x:v>
       </x:c>
       <x:c r="C22" s="0">
         <x:v>2</x:v>
@@ -3721,7 +3427,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>375</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>2</x:v>
@@ -3748,21 +3454,21 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
     <x:pageSetUpPr/>
   </x:sheetPr>
-  <x:dimension ref="A1:F6"/>
+  <x:dimension ref="A1:G13"/>
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="40.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16.567768" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="143.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="102.424911" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="56.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="4" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="41.996339" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="60.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="inlineStr">
         <x:is>
-          <x:t>stageId</x:t>
+          <x:t>themeId</x:t>
         </x:is>
       </x:c>
       <x:c r="B1" s="1" t="inlineStr">
@@ -3772,159 +3478,390 @@
       </x:c>
       <x:c r="C1" s="1" t="inlineStr">
         <x:is>
-          <x:t>mapWidth</x:t>
+          <x:t>minLevel</x:t>
         </x:is>
       </x:c>
       <x:c r="D1" s="1" t="inlineStr">
         <x:is>
-          <x:t>mapHeight</x:t>
+          <x:t>maxLevel</x:t>
         </x:is>
       </x:c>
       <x:c r="E1" s="1" t="inlineStr">
         <x:is>
-          <x:t>prefabPath</x:t>
+          <x:t>weight</x:t>
         </x:is>
       </x:c>
       <x:c r="F1" s="1" t="inlineStr">
         <x:is>
-          <x:t>islandCellSpan</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6">
+          <x:t>maxPerRun</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>members</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="inlineStr">
         <x:is>
+          <x:t>string</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>string</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="1" t="inlineStr">
+        <x:is>
           <x:t>int</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="1" t="inlineStr">
-        <x:is>
-          <x:t>string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="1" t="inlineStr">
+      <x:c r="D2" s="1" t="inlineStr">
         <x:is>
           <x:t>int</x:t>
         </x:is>
       </x:c>
-      <x:c r="D2" s="1" t="inlineStr">
+      <x:c r="E2" s="1" t="inlineStr">
         <x:is>
           <x:t>int</x:t>
         </x:is>
       </x:c>
-      <x:c r="E2" s="1" t="inlineStr">
-        <x:is>
-          <x:t>string</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F2" s="1" t="inlineStr">
         <x:is>
           <x:t>int</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
+      <x:c r="G2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>string[]</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="inlineStr">
         <x:is>
-          <x:t>关卡 Id（主键，1 起；每关一张独立的浮空岛地图）</x:t>
+          <x:t>主题 Id（主键，camelCase）。一个主题 = 一组「互相加分」的建筑配方，选组时一组只出一个主题的建筑</x:t>
         </x:is>
       </x:c>
       <x:c r="B3" s="1" t="inlineStr">
         <x:is>
-          <x:t>关卡显示名</x:t>
+          <x:t>显示名（手牌选组按钮上会显示，让玩家一眼看懂这组是干什么的）</x:t>
         </x:is>
       </x:c>
       <x:c r="C3" s="1" t="inlineStr">
         <x:is>
-          <x:t>本关地图宽（格；需求=250。地图稀疏存储，岛屿只占其中一部分，其余为虚空）</x:t>
+          <x:t>最早出现等级（含）。主题按阶段解锁：前期生产（矿业/农业）→ 中期居住商业 → 后期物流港口</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" s="1" t="inlineStr">
         <x:is>
-          <x:t>本关地图高（格；需求=250）</x:t>
+          <x:t>最晚出现等级（含）。0 = 一直可用</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" s="1" t="inlineStr">
         <x:is>
-          <x:t>关卡岛屿模型/场景资源路径（Resources 相对路径或 Addressables key，与 BuildingVariant.prefabPath 同口径；空=白模占位）。由菜单 Tools/美术/生成白模 Prefab 生成到 Assets/Resources/Prefab/Stage/</x:t>
+          <x:t>同一等级内被抽中的权重（正整数）。同一级的两组必定是两个不同主题，抽中后不放回</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="1" t="inlineStr">
         <x:is>
-          <x:t>岛屿模型入场时缩放到的可玩跨度（格）：把模型 XZ 包围盒的长边等比缩放到 islandCellSpan × GameConfig.cellSize 米，居中放在地图中心。地形刷子按缩放后的岛面轮廓描摹地块</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
-      <x:c r="A4" s="0">
+          <x:t>本主题一局最多被玩家选中几次，选满后不再进候选池；0 = 不限。用来给地标建筑封顶——市民中心配 1:1:1 且本列填 3，一局就最多 3 个市民中心</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="1" t="inlineStr">
+        <x:is>
+          <x:t>成员配方：变体Id:权重[:最少[:最多]]，多条用|分隔。权重=剩余名额里的抽取权重（核心建筑权重高=出得多），最少=本组保底几栋（默认 0），最多=本组上限（默认 0 = 不限）。例 miningStation_01:6:2:3|workshop_01:2:1:1 = 采矿站 2~3 栋、工坊恰好 1 栋</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>mining</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>矿业开采</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="0">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="inlineStr">
-        <x:is>
-          <x:t>浮空岛·一</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>250</x:v>
-      </x:c>
       <x:c r="D4" s="0">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="inlineStr">
-        <x:is>
-          <x:t>Prefab/Stage/stage_01</x:t>
-        </x:is>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E4" s="0">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
-      <x:c r="A5" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>miningStation_01:6:2:3|workshop_01:2:1:1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>farmland</x:t>
+        </x:is>
       </x:c>
       <x:c r="B5" s="0" t="inlineStr">
         <x:is>
-          <x:t>浮空岛·二</x:t>
+          <x:t>农田耕作</x:t>
         </x:is>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>250</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="inlineStr">
-        <x:is>
-          <x:t>Prefab/Stage/stage_02</x:t>
-        </x:is>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E5" s="0">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
-      <x:c r="A6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>farm_01:6:2:4|windmill_01:2:0:1|sail_01:2:0:1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>granaryDepot</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>粮储基地</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="0">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="inlineStr">
-        <x:is>
-          <x:t>浮空岛·三</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>250</x:v>
-      </x:c>
       <x:c r="D6" s="0">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="inlineStr">
-        <x:is>
-          <x:t>Prefab/Stage/stage_03</x:t>
-        </x:is>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E6" s="0">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>farm_01:5:2:3|granary_01:3:1:2|windmill_01:1:0:1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:7">
+      <x:c r="A7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>residentialBlock</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>居民街区</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E7" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>residence_01:5:2:3|residence_02:3:0:2|residence_03:3:0:2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="0" t="inlineStr">
+        <x:is>
+          <x:t>commerceStreet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="0" t="inlineStr">
+        <x:is>
+          <x:t>商业街</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D8" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E8" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:7">
+      <x:c r="A9" s="0" t="inlineStr">
+        <x:is>
+          <x:t>civicCenter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="0" t="inlineStr">
+        <x:is>
+          <x:t>市民中心区</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="inlineStr">
+        <x:is>
+          <x:t>citizenCenter_01:1:1:1|residence_01:5:1:3|residence_03:3:0:2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
+      <x:c r="A10" s="0" t="inlineStr">
+        <x:is>
+          <x:t>windPower</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="0" t="inlineStr">
+        <x:is>
+          <x:t>风能塔群</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D10" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E10" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="inlineStr">
+        <x:is>
+          <x:t>potentialTower_01:4:1:2|windmill_01:2:1:1|sail_01:3:1:2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
+      <x:c r="A11" s="0" t="inlineStr">
+        <x:is>
+          <x:t>logisticsNet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="0" t="inlineStr">
+        <x:is>
+          <x:t>物流网络</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D11" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E11" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="inlineStr">
+        <x:is>
+          <x:t>logisticsPoint_01:6:2:3|logisticsHub_01:2:1:1|workshop_01:2:0:1</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:7">
+      <x:c r="A12" s="0" t="inlineStr">
+        <x:is>
+          <x:t>harbor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="0" t="inlineStr">
+        <x:is>
+          <x:t>港口船坞</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D12" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E12" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="inlineStr">
+        <x:is>
+          <x:t>dock_01:2:1:1|workshop_01:3:1:2|logisticsPoint_01:4:1:2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:7">
+      <x:c r="A13" s="0" t="inlineStr">
+        <x:is>
+          <x:t>windVaneQuarter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="0" t="inlineStr">
+        <x:is>
+          <x:t>风向标社区</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D13" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E13" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="inlineStr">
+        <x:is>
+          <x:t>windVane_01:2:1:2|residence_01:5:2:3</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3942,239 +3879,240 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
     <x:pageSetUpPr/>
   </x:sheetPr>
-  <x:dimension ref="A1:D11"/>
+  <x:dimension ref="A1:I6"/>
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25.139196" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="121.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="143.567768" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="102.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="89.853482" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="135.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="100.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="1" t="inlineStr">
         <x:is>
-          <x:t>key</x:t>
+          <x:t>stageId</x:t>
         </x:is>
       </x:c>
       <x:c r="B1" s="1" t="inlineStr">
         <x:is>
-          <x:t>type</x:t>
+          <x:t>nameCn</x:t>
         </x:is>
       </x:c>
       <x:c r="C1" s="1" t="inlineStr">
         <x:is>
-          <x:t>value</x:t>
+          <x:t>mapWidth</x:t>
         </x:is>
       </x:c>
       <x:c r="D1" s="1" t="inlineStr">
         <x:is>
-          <x:t>desc</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>cellSize</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="0">
+          <x:t>mapHeight</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>prefabPath</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="1" t="inlineStr">
+        <x:is>
+          <x:t>islandCellSpan</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
+      <x:c r="A2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>string</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>string</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" s="1" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
+      <x:c r="A3" s="1" t="inlineStr">
+        <x:is>
+          <x:t>关卡 Id（主键，1 起；每关一张独立的浮空岛地图）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="1" t="inlineStr">
+        <x:is>
+          <x:t>关卡显示名</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="1" t="inlineStr">
+        <x:is>
+          <x:t>本关地图宽（格；需求=250。地图稀疏存储，岛屿只占其中一部分，其余为虚空）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="1" t="inlineStr">
+        <x:is>
+          <x:t>本关地图高（格；需求=250）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="1" t="inlineStr">
+        <x:is>
+          <x:t>关卡岛屿模型/场景资源路径（Resources 相对路径或 Addressables key，与 BuildingVariant.prefabPath 同口径；空=白模占位）。由菜单 Tools/美术/生成白模 Prefab 生成到 Assets/Resources/Prefab/Stage/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" s="1" t="inlineStr">
+        <x:is>
+          <x:t>岛屿模型入场时缩放到的可玩跨度（格）：把模型 XZ 包围盒的长边等比缩放到 islandCellSpan × GameConfig.cellSize 米，居中放在地图中心。地形刷子按缩放后的岛面轮廓描摹地块</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
+      <x:c r="A4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>浮空岛·一</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Prefab/Stage/stage_01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G4" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H4" s="0">
+        <x:v>2600</x:v>
+      </x:c>
+      <x:c r="I4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
+      <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>一个格子的世界边长（单位：米）。必须与 EGB 网格预制体的 cellSize 一致（当前 2）；模型导入后处理按它把建筑缩放到 footprint 对应的格数</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0" t="inlineStr">
-        <x:is>
-          <x:t>totalLevels</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="0" t="inlineStr">
-        <x:is>
-          <x:t>int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="inlineStr">
-        <x:is>
-          <x:t>每局总等级数（§4.1=20）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0" t="inlineStr">
-        <x:is>
-          <x:t>scoreToGoldRatio</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="0" t="inlineStr">
-        <x:is>
-          <x:t>float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="inlineStr">
-        <x:is>
-          <x:t>正分转金币比例（即时建造分×比例=金币；负分不倒扣 §3.3；0=待定）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0" t="inlineStr">
-        <x:is>
-          <x:t>freeRefreshCount</x:t>
-        </x:is>
-      </x:c>
       <x:c r="B5" s="0" t="inlineStr">
         <x:is>
-          <x:t>int</x:t>
+          <x:t>浮空岛·二</x:t>
         </x:is>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="inlineStr">
-        <x:is>
-          <x:t>每局免费刷新建筑组次数（随机保护 §4.3；0=待定）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0" t="inlineStr">
-        <x:is>
-          <x:t>refreshCostGold</x:t>
-        </x:is>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Prefab/Stage/stage_02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G5" s="0">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H5" s="0">
+        <x:v>1250</x:v>
+      </x:c>
+      <x:c r="I5" s="0">
+        <x:v>0.72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
+      <x:c r="A6" s="0">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="inlineStr">
         <x:is>
-          <x:t>int</x:t>
+          <x:t>浮空岛·三</x:t>
         </x:is>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="inlineStr">
-        <x:is>
-          <x:t>免费次数用完后每次刷新的金币费用（§4.3；0=待定）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
-      <x:c r="A7" s="0" t="inlineStr">
-        <x:is>
-          <x:t>skipPenaltyScore</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="0" t="inlineStr">
-        <x:is>
-          <x:t>int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>-20</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="inlineStr">
-        <x:is>
-          <x:t>跳过一栋无法合法放置建筑的扣分（负值，§4.3 保护机制；0=不启用）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:4">
-      <x:c r="A8" s="0" t="inlineStr">
-        <x:is>
-          <x:t>guaranteeEasyBuilding</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="0" t="inlineStr">
-        <x:is>
-          <x:t>bool</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="0" t="inlineStr">
-        <x:is>
-          <x:t>TRUE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="0" t="inlineStr">
-        <x:is>
-          <x:t>是否保证每组至少一栋容易放置的建筑（§4.3 保护机制）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:4">
-      <x:c r="A9" s="0" t="inlineStr">
-        <x:is>
-          <x:t>giantWindmillGenericScore</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="0" t="inlineStr">
-        <x:is>
-          <x:t>int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="inlineStr">
-        <x:is>
-          <x:t>巨型风车通用加分——范围内任意普通建筑获得；有专属条目（BuildingMapElement.exclusive=TRUE）的建筑用专属分替代不叠加（§6；0=待定）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
-      <x:c r="A10" s="0" t="inlineStr">
-        <x:is>
-          <x:t>layerHeightFactor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="0" t="inlineStr">
-        <x:is>
-          <x:t>float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="inlineStr">
-        <x:is>
-          <x:t>层高折算系数 k（决策 26）：建筑/元素的影响范围为球形，三维欧氏距离 = √(水平格距² + (高度层差×k)²)。表现层的 EGB verticalGridHeight = k × cellSize，两边必须同一个 k（当前预制体 2/2 → k=1）</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4">
-      <x:c r="A11" s="0" t="inlineStr">
-        <x:is>
-          <x:t>anchorDockDecayPercents</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="0" t="inlineStr">
-        <x:is>
-          <x:t>float[]</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="0" t="inlineStr">
-        <x:is>
-          <x:t>1|0.5|0.25|0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="0" t="inlineStr">
-        <x:is>
-          <x:t>同一锚点下第 N 座船坞的锚点收益倍率（§12.8 已定：1|0.5|0.25|0，第 4 座及以后 0）</x:t>
-        </x:is>
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Prefab/Stage/stage_03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G6" s="0">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H6" s="0">
+        <x:v>1750</x:v>
+      </x:c>
+      <x:c r="I6" s="0">
+        <x:v>0.82</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4192,13 +4130,13 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
     <x:pageSetUpPr/>
   </x:sheetPr>
-  <x:dimension ref="A1:D6"/>
+  <x:dimension ref="A1:D9"/>
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20.567768" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="4.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="5.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="74.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.996339" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="121.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -4226,27 +4164,27 @@
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="inlineStr">
         <x:is>
-          <x:t>maxWindLevel</x:t>
+          <x:t>cellSize</x:t>
         </x:is>
       </x:c>
       <x:c r="B2" s="0" t="inlineStr">
         <x:is>
-          <x:t>int</x:t>
+          <x:t>float</x:t>
         </x:is>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="0" t="inlineStr">
         <x:is>
-          <x:t>风力等级上限（合并后不超过此级，§8.5=5）</x:t>
+          <x:t>一个格子的世界边长（单位：米）。必须与 EGB 网格预制体的 cellSize 一致（当前 2）；模型导入后处理按它把建筑缩放到 footprint 对应的格数</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="inlineStr">
         <x:is>
-          <x:t>initialWindLevelMin</x:t>
+          <x:t>totalLevels</x:t>
         </x:is>
       </x:c>
       <x:c r="B3" s="0" t="inlineStr">
@@ -4255,18 +4193,18 @@
         </x:is>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="0" t="inlineStr">
         <x:is>
-          <x:t>初始风强度随机下限（1~5；§20 待定）</x:t>
+          <x:t>每局总等级数（§4.1=20）</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="inlineStr">
         <x:is>
-          <x:t>initialWindLevelMax</x:t>
+          <x:t>freeRefreshCount</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" s="0" t="inlineStr">
@@ -4275,18 +4213,18 @@
         </x:is>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="0" t="inlineStr">
         <x:is>
-          <x:t>初始风强度随机上限（1~5；§20 待定）</x:t>
+          <x:t>每局免费刷新建筑组次数（随机保护 §4.3；0=待定）</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="inlineStr">
         <x:is>
-          <x:t>initialWindLengthMin</x:t>
+          <x:t>skipPenaltyScore</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" s="0" t="inlineStr">
@@ -4295,31 +4233,95 @@
         </x:is>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>8</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="D5" s="0" t="inlineStr">
         <x:is>
-          <x:t>初始风传播长度随机下限（格；§20 待定。初始风数量在 MapElement.windSource 的 countMin/countMax）</x:t>
+          <x:t>跳过一栋无法合法放置建筑的扣分（负值，§4.3 保护机制；0=不启用）</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="inlineStr">
         <x:is>
-          <x:t>initialWindLengthMax</x:t>
+          <x:t>guaranteeEasyBuilding</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="0" t="inlineStr">
         <x:is>
+          <x:t>bool</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>TRUE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="0" t="inlineStr">
+        <x:is>
+          <x:t>是否保证每组至少一栋容易放置的建筑（§4.3 保护机制）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>giantWindmillGenericScore</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="0" t="inlineStr">
+        <x:is>
           <x:t>int</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="0">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="inlineStr">
-        <x:is>
-          <x:t>初始风传播长度随机上限（格；§20 待定）</x:t>
+      <x:c r="C7" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="inlineStr">
+        <x:is>
+          <x:t>巨型风车通用加分——范围内任意普通建筑获得；有专属条目（BuildingMapElement.exclusive=TRUE）的建筑用专属分替代不叠加（§6；0=待定）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:4">
+      <x:c r="A8" s="0" t="inlineStr">
+        <x:is>
+          <x:t>layerHeightFactor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="0" t="inlineStr">
+        <x:is>
+          <x:t>float</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="inlineStr">
+        <x:is>
+          <x:t>层高折算系数 k（决策 26）：建筑/元素的影响范围为球形，三维欧氏距离 = √(水平格距² + (高度层差×k)²)。表现层的 EGB verticalGridHeight = k × cellSize，两边必须同一个 k（当前预制体 2/2 → k=1）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:4">
+      <x:c r="A9" s="0" t="inlineStr">
+        <x:is>
+          <x:t>anchorDockDecayPercents</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="0" t="inlineStr">
+        <x:is>
+          <x:t>float[]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="0" t="inlineStr">
+        <x:is>
+          <x:t>1|0.5|0.25|0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="0" t="inlineStr">
+        <x:is>
+          <x:t>同一锚点下第 N 座船坞的锚点收益倍率（§12.8 已定：1|0.5|0.25|0，第 4 座及以后 0）</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>######|######|######|######|######|######</t>
+          <t>####|####|####|####|####|####|####</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">

--- a/FloatingIsLand/Tables/FloatingIsland.xlsx
+++ b/FloatingIsLand/Tables/FloatingIsland.xlsx
@@ -3686,7 +3686,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
